--- a/1_BBS/BBS_stakeholders.XLSX
+++ b/1_BBS/BBS_stakeholders.XLSX
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anna\Desktop\My_files\University\School21\BSA02_Requirements.ID_1361442-1\src\BBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anna\Desktop\My_files\University\School21\portfolio_analyst\1_BBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715CBC48-F59C-4521-B0EA-5428F8023B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E17B87-5567-4B11-A0BF-D0CDDAC7DB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Список стейкхолдеров" sheetId="1" r:id="rId1"/>
@@ -231,9 +231,6 @@
     <t>Снизить трудозатраты сотрудников на дозвоны и запись клиентов</t>
   </si>
   <si>
-    <t>Высокие неравномерные трудозатраты (пиковые периоды) на запись по телефону,</t>
-  </si>
-  <si>
     <t>Средний чек</t>
   </si>
   <si>
@@ -246,18 +243,12 @@
     <t>В пиковые периоды менеджер не успевает обработать звонки для записи на услуги</t>
   </si>
   <si>
-    <t>Клиент часто не приходит на услугу, не помнит время записи</t>
-  </si>
-  <si>
     <t>Клиенты при записи по телефону не видят полного списка услуг</t>
   </si>
   <si>
     <t>Предоставляемые услуги и их стоимость</t>
   </si>
   <si>
-    <t>Видеть отзывы на услуги и мастеров, иметь возможность выбрать лучшую</t>
-  </si>
-  <si>
     <t>Долгие ответы менеджера на вопросы</t>
   </si>
   <si>
@@ -267,9 +258,6 @@
     <t>Получить напоминание о записи чтобы не пропустить</t>
   </si>
   <si>
-    <t>Отсутствие напоминания об услуге, пропуск записи</t>
-  </si>
-  <si>
     <t>Скорость ответа на вопросы</t>
   </si>
   <si>
@@ -405,9 +393,6 @@
     <t>Качество кода</t>
   </si>
   <si>
-    <t>Оптимизировать приложение, исправлять баги</t>
-  </si>
-  <si>
     <t>Функционал закрывает недостаточно потребностей</t>
   </si>
   <si>
@@ -474,12 +459,6 @@
     <t>Невозможность подтвердить выполнение уборки</t>
   </si>
   <si>
-    <t>Просмотр информации о полученных услугах, их датах, мастерах и др.</t>
-  </si>
-  <si>
-    <t>Клиент не помнит когда была последняя запись, не может на основе этого принять решение</t>
-  </si>
-  <si>
     <t>Клиенту трудно записаться/дозвониться до менеджера</t>
   </si>
   <si>
@@ -504,9 +483,6 @@
     <t>Отсутствие информации о появлении новых услуг</t>
   </si>
   <si>
-    <t>Новые услуги не пользуются популярностью, так как о них никто не знает</t>
-  </si>
-  <si>
     <t>Много отмен из-за отсутствия напоминаний клиентам</t>
   </si>
   <si>
@@ -516,9 +492,6 @@
     <t>Управляющий</t>
   </si>
   <si>
-    <t>Ручное составление расписания, возникновение ошибок и дублей</t>
-  </si>
-  <si>
     <t>Множество ручной рутинной работы</t>
   </si>
   <si>
@@ -552,9 +525,6 @@
     <t>Поддержание актуальности аккаунтов</t>
   </si>
   <si>
-    <t>Устаревание информации, накопление лишних аккаунтов</t>
-  </si>
-  <si>
     <t>У клиентов и посетителей возникают проблемы с работой приложения</t>
   </si>
   <si>
@@ -595,6 +565,36 @@
   </si>
   <si>
     <t>Отсутствие отчетности</t>
+  </si>
+  <si>
+    <t>Высокие неравномерные трудозатраты (пиковые периоды) на запись по телефону;</t>
+  </si>
+  <si>
+    <t>Клиент часто не приходит на услугу; не помнит время записи</t>
+  </si>
+  <si>
+    <t>Видеть отзывы на услуги и мастеров; иметь возможность выбрать лучшую</t>
+  </si>
+  <si>
+    <t>Отсутствие напоминания об услуге; пропуск записи</t>
+  </si>
+  <si>
+    <t>Клиент не помнит когда была последняя запись; не может на основе этого принять решение</t>
+  </si>
+  <si>
+    <t>Просмотр информации о полученных услугах; их датах; мастерах и др.</t>
+  </si>
+  <si>
+    <t>Новые услуги не пользуются популярностью; так как о них никто не знает</t>
+  </si>
+  <si>
+    <t>Ручное составление расписания; возникновение ошибок и дублей</t>
+  </si>
+  <si>
+    <t>Устаревание информации; накопление лишних аккаунтов</t>
+  </si>
+  <si>
+    <t>Оптимизировать приложение; исправлять баги</t>
   </si>
 </sst>
 </file>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
@@ -1630,15 +1630,15 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>29</v>
@@ -1656,7 +1656,7 @@
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1774,7 +1774,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>63</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1782,19 +1782,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" s="1">
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1805,7 +1805,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1816,7 +1816,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1827,7 +1827,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1841,19 +1841,19 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1861,19 +1861,19 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G10" s="1">
         <v>2</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1881,19 +1881,19 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G11" s="1">
         <v>3</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -1901,19 +1901,19 @@
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G12" s="1">
         <v>4</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1921,19 +1921,19 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1941,13 +1941,13 @@
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G14" s="1">
         <v>6</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1955,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G15" s="1">
         <v>7</v>
@@ -1966,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1974,7 +1974,7 @@
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -1988,19 +1988,19 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2008,19 +2008,19 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G19" s="1">
         <v>2</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2028,19 +2028,19 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2048,19 +2048,19 @@
         <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2068,7 +2068,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2082,19 +2082,19 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2102,19 +2102,19 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G24" s="1">
         <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2122,19 +2122,19 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G25" s="1">
         <v>3</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2142,13 +2142,13 @@
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G26" s="1">
         <v>4</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2156,13 +2156,13 @@
         <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G27" s="1">
         <v>5</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2170,13 +2170,13 @@
         <v>6</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G28" s="1">
         <v>6</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2190,19 +2190,19 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2210,19 +2210,19 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G30" s="1">
         <v>2</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2230,19 +2230,19 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G31" s="1">
         <v>3</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -2250,16 +2250,16 @@
         <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E32" s="1">
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -2267,7 +2267,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -2275,7 +2275,7 @@
         <v>6</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2283,25 +2283,25 @@
         <v>25</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2309,19 +2309,19 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2329,19 +2329,19 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G37" s="1">
         <v>3</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2349,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -2357,7 +2357,7 @@
         <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2365,7 +2365,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2379,19 +2379,19 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2399,13 +2399,13 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G42" s="1">
         <v>2</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2413,7 +2413,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2427,19 +2427,19 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G44" s="1">
         <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2447,19 +2447,19 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E45" s="1">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G45" s="1">
-        <v>2</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -2467,13 +2467,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E46" s="1">
         <v>3</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -2481,12 +2481,12 @@
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F48" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -2494,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2508,19 +2508,19 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G50" s="1">
         <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2528,19 +2528,19 @@
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -2548,13 +2548,13 @@
         <v>3</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G52" s="1">
         <v>3</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -2562,7 +2562,7 @@
         <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2576,19 +2576,19 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G54" s="1">
         <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2596,19 +2596,19 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2616,13 +2616,13 @@
         <v>3</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G56" s="1">
         <v>3</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2636,77 +2636,77 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="D58" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G58" s="1">
         <v>2</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="F60" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="G60" s="1">
         <v>2</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="F61" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>29</v>
@@ -2715,19 +2715,19 @@
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -2735,13 +2735,13 @@
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G63" s="1">
         <v>2</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
